--- a/arquivos/id_tecnologia_facilidades.xlsx
+++ b/arquivos/id_tecnologia_facilidades.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29231"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29328"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\F257064\Documents\Codes\atualizacao nfv automatico\NEW_NFV\arquivos\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\F257064\Documents\Codes\atualizacao automacao lote\AUTMACAO_LOTE\arquivos\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5B3D3CED-1077-4EFA-9A73-F10968C9078B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ACE69BCB-2272-4298-92F1-EB2EFAF4F4FB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-24120" yWindow="-120" windowWidth="24240" windowHeight="13020" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="123" uniqueCount="61">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="123" uniqueCount="62">
   <si>
     <t>FACILIDADE</t>
   </si>
@@ -206,9 +206,6 @@
     <t>RADIO IP</t>
   </si>
   <si>
-    <t>TERCEIROS BL</t>
-  </si>
-  <si>
     <t>FO GPON_RESID ETH PV</t>
   </si>
   <si>
@@ -219,6 +216,12 @@
   </si>
   <si>
     <t>CLARO BRASIL</t>
+  </si>
+  <si>
+    <t>TERCEIRO ETH</t>
+  </si>
+  <si>
+    <t>TERCEIRO BL</t>
   </si>
 </sst>
 </file>
@@ -584,7 +587,7 @@
         <v>4</v>
       </c>
       <c r="F2" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="G2">
         <v>8</v>
@@ -607,7 +610,7 @@
         <v>34</v>
       </c>
       <c r="F3" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="G3">
         <v>8</v>
@@ -630,7 +633,7 @@
         <v>35</v>
       </c>
       <c r="F4" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="G4">
         <v>8</v>
@@ -653,7 +656,7 @@
         <v>38</v>
       </c>
       <c r="F5" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="G5">
         <v>8</v>
@@ -676,7 +679,7 @@
         <v>37</v>
       </c>
       <c r="F6" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="G6">
         <v>8</v>
@@ -699,7 +702,7 @@
         <v>36</v>
       </c>
       <c r="F7" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="G7">
         <v>8</v>
@@ -719,10 +722,10 @@
         <v>52</v>
       </c>
       <c r="E8" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="F8" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="G8">
         <v>8</v>
@@ -742,7 +745,7 @@
         <v>5</v>
       </c>
       <c r="F9" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="G9">
         <v>8</v>
@@ -765,7 +768,7 @@
         <v>8</v>
       </c>
       <c r="F10" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="G10">
         <v>8</v>
@@ -788,7 +791,7 @@
         <v>9</v>
       </c>
       <c r="F11" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="G11">
         <v>8</v>
@@ -811,7 +814,7 @@
         <v>11</v>
       </c>
       <c r="F12" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="G12">
         <v>8</v>
@@ -834,7 +837,7 @@
         <v>12</v>
       </c>
       <c r="F13" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="G13">
         <v>8</v>
@@ -857,7 +860,7 @@
         <v>14</v>
       </c>
       <c r="F14" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="G14">
         <v>8</v>
@@ -880,7 +883,7 @@
         <v>16</v>
       </c>
       <c r="F15" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="G15">
         <v>8</v>
@@ -903,7 +906,7 @@
         <v>41</v>
       </c>
       <c r="F16" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="G16">
         <v>8</v>
@@ -926,7 +929,7 @@
         <v>54</v>
       </c>
       <c r="F17" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="G17">
         <v>8</v>
@@ -949,7 +952,7 @@
         <v>42</v>
       </c>
       <c r="F18" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="G18">
         <v>8</v>
@@ -972,7 +975,7 @@
         <v>43</v>
       </c>
       <c r="F19" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="G19">
         <v>8</v>
@@ -989,10 +992,10 @@
         <v>40</v>
       </c>
       <c r="E20" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="F20" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="G20">
         <v>8</v>
@@ -1009,10 +1012,10 @@
         <v>40</v>
       </c>
       <c r="E21" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="F21" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="G21">
         <v>8</v>
@@ -1035,7 +1038,7 @@
         <v>53</v>
       </c>
       <c r="F22" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="G22">
         <v>8</v>
@@ -1058,7 +1061,7 @@
         <v>46</v>
       </c>
       <c r="F23" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="G23">
         <v>8</v>
@@ -1075,7 +1078,7 @@
         <v>47</v>
       </c>
       <c r="E24" t="s">
-        <v>47</v>
+        <v>60</v>
       </c>
     </row>
     <row r="25" spans="1:7" x14ac:dyDescent="0.3">
@@ -1089,7 +1092,7 @@
         <v>47</v>
       </c>
       <c r="E25" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
     </row>
     <row r="26" spans="1:7" x14ac:dyDescent="0.3">
@@ -1106,7 +1109,7 @@
         <v>55</v>
       </c>
       <c r="F26" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="G26">
         <v>8</v>

--- a/arquivos/id_tecnologia_facilidades.xlsx
+++ b/arquivos/id_tecnologia_facilidades.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\F257064\Documents\Codes\atualizacao automacao lote\AUTMACAO_LOTE\arquivos\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ACE69BCB-2272-4298-92F1-EB2EFAF4F4FB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1D1F90B8-9988-4E2E-A2AB-E2CE97098F48}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-24120" yWindow="-120" windowWidth="24240" windowHeight="13020" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -50,9 +50,6 @@
     <t>4G</t>
   </si>
   <si>
-    <t>LTE (4G)</t>
-  </si>
-  <si>
     <t>ADE</t>
   </si>
   <si>
@@ -222,6 +219,9 @@
   </si>
   <si>
     <t>TERCEIRO BL</t>
+  </si>
+  <si>
+    <t>LTE(4G)</t>
   </si>
 </sst>
 </file>
@@ -552,7 +552,7 @@
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B1" t="s">
         <v>0</v>
@@ -561,16 +561,16 @@
         <v>1</v>
       </c>
       <c r="D1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="E1" t="s">
         <v>2</v>
       </c>
       <c r="F1" t="s">
+        <v>47</v>
+      </c>
+      <c r="G1" t="s">
         <v>48</v>
-      </c>
-      <c r="G1" t="s">
-        <v>49</v>
       </c>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.3">
@@ -584,10 +584,10 @@
         <v>3</v>
       </c>
       <c r="E2" t="s">
-        <v>4</v>
+        <v>61</v>
       </c>
       <c r="F2" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="G2">
         <v>8</v>
@@ -598,19 +598,19 @@
         <v>19</v>
       </c>
       <c r="B3" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C3" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="D3" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="E3" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="F3" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="G3">
         <v>8</v>
@@ -621,19 +621,19 @@
         <v>19</v>
       </c>
       <c r="B4" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C4" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="D4" t="s">
+        <v>33</v>
+      </c>
+      <c r="E4" t="s">
         <v>34</v>
       </c>
-      <c r="E4" t="s">
-        <v>35</v>
-      </c>
       <c r="F4" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="G4">
         <v>8</v>
@@ -644,19 +644,19 @@
         <v>34</v>
       </c>
       <c r="B5" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C5" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="D5" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="E5" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="F5" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="G5">
         <v>8</v>
@@ -667,19 +667,19 @@
         <v>34</v>
       </c>
       <c r="B6" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C6" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="D6" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="E6" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="F6" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="G6">
         <v>8</v>
@@ -690,19 +690,19 @@
         <v>34</v>
       </c>
       <c r="B7" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C7" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="D7" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="E7" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="F7" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="G7">
         <v>8</v>
@@ -713,19 +713,19 @@
         <v>50</v>
       </c>
       <c r="B8" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="C8" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="D8" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="E8" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="F8" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="G8">
         <v>8</v>
@@ -736,16 +736,16 @@
         <v>2</v>
       </c>
       <c r="B9" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D9" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E9" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F9" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="G9">
         <v>8</v>
@@ -756,19 +756,19 @@
         <v>7</v>
       </c>
       <c r="B10" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C10" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D10" t="s">
+        <v>6</v>
+      </c>
+      <c r="E10" t="s">
         <v>7</v>
       </c>
-      <c r="E10" t="s">
-        <v>8</v>
-      </c>
       <c r="F10" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="G10">
         <v>8</v>
@@ -779,19 +779,19 @@
         <v>7</v>
       </c>
       <c r="B11" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C11" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D11" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E11" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F11" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="G11">
         <v>8</v>
@@ -802,19 +802,19 @@
         <v>8</v>
       </c>
       <c r="B12" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C12" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="D12" t="s">
+        <v>9</v>
+      </c>
+      <c r="E12" t="s">
         <v>10</v>
       </c>
-      <c r="E12" t="s">
-        <v>11</v>
-      </c>
       <c r="F12" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="G12">
         <v>8</v>
@@ -825,19 +825,19 @@
         <v>8</v>
       </c>
       <c r="B13" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C13" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D13" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E13" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="F13" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="G13">
         <v>8</v>
@@ -848,19 +848,19 @@
         <v>6</v>
       </c>
       <c r="B14" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C14" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D14" t="s">
+        <v>12</v>
+      </c>
+      <c r="E14" t="s">
         <v>13</v>
       </c>
-      <c r="E14" t="s">
-        <v>14</v>
-      </c>
       <c r="F14" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="G14">
         <v>8</v>
@@ -871,19 +871,19 @@
         <v>5</v>
       </c>
       <c r="B15" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="C15" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="D15" t="s">
+        <v>14</v>
+      </c>
+      <c r="E15" t="s">
         <v>15</v>
       </c>
-      <c r="E15" t="s">
-        <v>16</v>
-      </c>
       <c r="F15" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="G15">
         <v>8</v>
@@ -894,19 +894,19 @@
         <v>16</v>
       </c>
       <c r="B16" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C16" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="D16" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="E16" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="F16" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="G16">
         <v>8</v>
@@ -917,19 +917,19 @@
         <v>16</v>
       </c>
       <c r="B17" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C17" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="D17" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="E17" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="F17" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="G17">
         <v>8</v>
@@ -940,19 +940,19 @@
         <v>16</v>
       </c>
       <c r="B18" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C18" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="D18" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="E18" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="F18" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="G18">
         <v>8</v>
@@ -963,19 +963,19 @@
         <v>12</v>
       </c>
       <c r="B19" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="C19" t="s">
+        <v>42</v>
+      </c>
+      <c r="D19" t="s">
         <v>43</v>
       </c>
-      <c r="D19" t="s">
-        <v>44</v>
-      </c>
       <c r="E19" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="F19" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="G19">
         <v>8</v>
@@ -986,16 +986,16 @@
         <v>35</v>
       </c>
       <c r="B20" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D20" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="E20" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="F20" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="G20">
         <v>8</v>
@@ -1006,16 +1006,16 @@
         <v>36</v>
       </c>
       <c r="B21" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D21" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="E21" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="F21" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="G21">
         <v>8</v>
@@ -1026,19 +1026,19 @@
         <v>40</v>
       </c>
       <c r="B22" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C22" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="D22" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="E22" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="F22" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="G22">
         <v>8</v>
@@ -1049,19 +1049,19 @@
         <v>40</v>
       </c>
       <c r="B23" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C23" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="D23" t="s">
+        <v>44</v>
+      </c>
+      <c r="E23" t="s">
         <v>45</v>
       </c>
-      <c r="E23" t="s">
-        <v>46</v>
-      </c>
       <c r="F23" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="G23">
         <v>8</v>
@@ -1072,13 +1072,13 @@
         <v>26</v>
       </c>
       <c r="B24" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D24" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="E24" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
     </row>
     <row r="25" spans="1:7" x14ac:dyDescent="0.3">
@@ -1086,13 +1086,13 @@
         <v>26</v>
       </c>
       <c r="B25" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D25" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="E25" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
     </row>
     <row r="26" spans="1:7" x14ac:dyDescent="0.3">
@@ -1100,16 +1100,16 @@
         <v>21</v>
       </c>
       <c r="B26" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="D26" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="E26" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="F26" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="G26">
         <v>8</v>

--- a/arquivos/id_tecnologia_facilidades.xlsx
+++ b/arquivos/id_tecnologia_facilidades.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\F257064\Documents\Codes\atualizacao automacao lote\AUTMACAO_LOTE\arquivos\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1D1F90B8-9988-4E2E-A2AB-E2CE97098F48}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F6D3B701-1004-4501-ABDB-9D00383EDAC6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-24120" yWindow="-120" windowWidth="24240" windowHeight="13020" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="123" uniqueCount="62">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="126" uniqueCount="62">
   <si>
     <t>FACILIDADE</t>
   </si>
@@ -203,9 +203,6 @@
     <t>RADIO IP</t>
   </si>
   <si>
-    <t>FO GPON_RESID ETH PV</t>
-  </si>
-  <si>
     <t>BANDA KA</t>
   </si>
   <si>
@@ -222,6 +219,9 @@
   </si>
   <si>
     <t>LTE(4G)</t>
+  </si>
+  <si>
+    <t>TERCEIRO SIMÉTRICO</t>
   </si>
 </sst>
 </file>
@@ -539,7 +539,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:G26"/>
+  <dimension ref="A1:G27"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="30.5546875" bestFit="1" customWidth="1"/>
@@ -584,10 +584,10 @@
         <v>3</v>
       </c>
       <c r="E2" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="F2" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="G2">
         <v>8</v>
@@ -610,7 +610,7 @@
         <v>33</v>
       </c>
       <c r="F3" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="G3">
         <v>8</v>
@@ -633,7 +633,7 @@
         <v>34</v>
       </c>
       <c r="F4" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="G4">
         <v>8</v>
@@ -656,7 +656,7 @@
         <v>37</v>
       </c>
       <c r="F5" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="G5">
         <v>8</v>
@@ -679,7 +679,7 @@
         <v>36</v>
       </c>
       <c r="F6" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="G6">
         <v>8</v>
@@ -702,7 +702,7 @@
         <v>35</v>
       </c>
       <c r="F7" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="G7">
         <v>8</v>
@@ -722,10 +722,10 @@
         <v>51</v>
       </c>
       <c r="E8" t="s">
-        <v>55</v>
+        <v>38</v>
       </c>
       <c r="F8" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="G8">
         <v>8</v>
@@ -745,7 +745,7 @@
         <v>4</v>
       </c>
       <c r="F9" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="G9">
         <v>8</v>
@@ -768,7 +768,7 @@
         <v>7</v>
       </c>
       <c r="F10" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="G10">
         <v>8</v>
@@ -791,7 +791,7 @@
         <v>8</v>
       </c>
       <c r="F11" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="G11">
         <v>8</v>
@@ -814,7 +814,7 @@
         <v>10</v>
       </c>
       <c r="F12" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="G12">
         <v>8</v>
@@ -837,7 +837,7 @@
         <v>11</v>
       </c>
       <c r="F13" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="G13">
         <v>8</v>
@@ -860,7 +860,7 @@
         <v>13</v>
       </c>
       <c r="F14" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="G14">
         <v>8</v>
@@ -883,7 +883,7 @@
         <v>15</v>
       </c>
       <c r="F15" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="G15">
         <v>8</v>
@@ -906,7 +906,7 @@
         <v>40</v>
       </c>
       <c r="F16" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="G16">
         <v>8</v>
@@ -929,7 +929,7 @@
         <v>53</v>
       </c>
       <c r="F17" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="G17">
         <v>8</v>
@@ -952,7 +952,7 @@
         <v>41</v>
       </c>
       <c r="F18" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="G18">
         <v>8</v>
@@ -975,7 +975,7 @@
         <v>42</v>
       </c>
       <c r="F19" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="G19">
         <v>8</v>
@@ -992,10 +992,10 @@
         <v>39</v>
       </c>
       <c r="E20" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="F20" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="G20">
         <v>8</v>
@@ -1012,10 +1012,10 @@
         <v>39</v>
       </c>
       <c r="E21" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="F21" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="G21">
         <v>8</v>
@@ -1038,7 +1038,7 @@
         <v>52</v>
       </c>
       <c r="F22" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="G22">
         <v>8</v>
@@ -1061,7 +1061,7 @@
         <v>45</v>
       </c>
       <c r="F23" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="G23">
         <v>8</v>
@@ -1078,7 +1078,7 @@
         <v>46</v>
       </c>
       <c r="E24" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
     </row>
     <row r="25" spans="1:7" x14ac:dyDescent="0.3">
@@ -1092,26 +1092,40 @@
         <v>46</v>
       </c>
       <c r="E25" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
     </row>
     <row r="26" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A26">
+        <v>26</v>
+      </c>
+      <c r="B26" t="s">
+        <v>29</v>
+      </c>
+      <c r="D26" t="s">
+        <v>46</v>
+      </c>
+      <c r="E26" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="27" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A27">
         <v>21</v>
       </c>
-      <c r="B26" t="s">
+      <c r="B27" t="s">
         <v>31</v>
       </c>
-      <c r="D26" t="s">
+      <c r="D27" t="s">
         <v>49</v>
       </c>
-      <c r="E26" t="s">
+      <c r="E27" t="s">
         <v>54</v>
       </c>
-      <c r="F26" t="s">
-        <v>58</v>
-      </c>
-      <c r="G26">
+      <c r="F27" t="s">
+        <v>57</v>
+      </c>
+      <c r="G27">
         <v>8</v>
       </c>
     </row>

--- a/arquivos/id_tecnologia_facilidades.xlsx
+++ b/arquivos/id_tecnologia_facilidades.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29328"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29426"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\F257064\Documents\Codes\atualizacao automacao lote\AUTMACAO_LOTE\arquivos\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F6D3B701-1004-4501-ABDB-9D00383EDAC6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D0B5DEDE-198E-4873-9797-08AB022C9436}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-24120" yWindow="-120" windowWidth="24240" windowHeight="13020" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Plan1" sheetId="1" r:id="rId1"/>
@@ -200,9 +200,6 @@
     <t>VIVAX</t>
   </si>
   <si>
-    <t>RADIO IP</t>
-  </si>
-  <si>
     <t>BANDA KA</t>
   </si>
   <si>
@@ -222,6 +219,9 @@
   </si>
   <si>
     <t>TERCEIRO SIMÉTRICO</t>
+  </si>
+  <si>
+    <t>EDD RADIO IP (LIVRE)</t>
   </si>
 </sst>
 </file>
@@ -584,10 +584,10 @@
         <v>3</v>
       </c>
       <c r="E2" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="F2" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="G2">
         <v>8</v>
@@ -610,7 +610,7 @@
         <v>33</v>
       </c>
       <c r="F3" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="G3">
         <v>8</v>
@@ -633,7 +633,7 @@
         <v>34</v>
       </c>
       <c r="F4" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="G4">
         <v>8</v>
@@ -656,7 +656,7 @@
         <v>37</v>
       </c>
       <c r="F5" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="G5">
         <v>8</v>
@@ -679,7 +679,7 @@
         <v>36</v>
       </c>
       <c r="F6" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="G6">
         <v>8</v>
@@ -702,7 +702,7 @@
         <v>35</v>
       </c>
       <c r="F7" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="G7">
         <v>8</v>
@@ -725,7 +725,7 @@
         <v>38</v>
       </c>
       <c r="F8" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="G8">
         <v>8</v>
@@ -745,7 +745,7 @@
         <v>4</v>
       </c>
       <c r="F9" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="G9">
         <v>8</v>
@@ -768,7 +768,7 @@
         <v>7</v>
       </c>
       <c r="F10" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="G10">
         <v>8</v>
@@ -791,7 +791,7 @@
         <v>8</v>
       </c>
       <c r="F11" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="G11">
         <v>8</v>
@@ -814,7 +814,7 @@
         <v>10</v>
       </c>
       <c r="F12" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="G12">
         <v>8</v>
@@ -837,7 +837,7 @@
         <v>11</v>
       </c>
       <c r="F13" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="G13">
         <v>8</v>
@@ -860,7 +860,7 @@
         <v>13</v>
       </c>
       <c r="F14" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="G14">
         <v>8</v>
@@ -883,7 +883,7 @@
         <v>15</v>
       </c>
       <c r="F15" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="G15">
         <v>8</v>
@@ -906,7 +906,7 @@
         <v>40</v>
       </c>
       <c r="F16" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="G16">
         <v>8</v>
@@ -929,7 +929,7 @@
         <v>53</v>
       </c>
       <c r="F17" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="G17">
         <v>8</v>
@@ -952,7 +952,7 @@
         <v>41</v>
       </c>
       <c r="F18" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="G18">
         <v>8</v>
@@ -975,7 +975,7 @@
         <v>42</v>
       </c>
       <c r="F19" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="G19">
         <v>8</v>
@@ -992,10 +992,10 @@
         <v>39</v>
       </c>
       <c r="E20" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="F20" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="G20">
         <v>8</v>
@@ -1012,10 +1012,10 @@
         <v>39</v>
       </c>
       <c r="E21" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="F21" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="G21">
         <v>8</v>
@@ -1038,7 +1038,7 @@
         <v>52</v>
       </c>
       <c r="F22" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="G22">
         <v>8</v>
@@ -1061,7 +1061,7 @@
         <v>45</v>
       </c>
       <c r="F23" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="G23">
         <v>8</v>
@@ -1078,7 +1078,7 @@
         <v>46</v>
       </c>
       <c r="E24" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
     </row>
     <row r="25" spans="1:7" x14ac:dyDescent="0.3">
@@ -1092,7 +1092,7 @@
         <v>46</v>
       </c>
       <c r="E25" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
     </row>
     <row r="26" spans="1:7" x14ac:dyDescent="0.3">
@@ -1106,12 +1106,12 @@
         <v>46</v>
       </c>
       <c r="E26" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
     </row>
     <row r="27" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A27">
-        <v>21</v>
+        <v>38</v>
       </c>
       <c r="B27" t="s">
         <v>31</v>
@@ -1120,10 +1120,10 @@
         <v>49</v>
       </c>
       <c r="E27" t="s">
-        <v>54</v>
+        <v>61</v>
       </c>
       <c r="F27" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="G27">
         <v>8</v>

--- a/arquivos/id_tecnologia_facilidades.xlsx
+++ b/arquivos/id_tecnologia_facilidades.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29426"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29822"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\F257064\Documents\Codes\atualizacao automacao lote\AUTMACAO_LOTE\arquivos\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D0B5DEDE-198E-4873-9797-08AB022C9436}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{33F72F34-4225-43A4-B751-28D99E0D46EF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-24120" yWindow="-120" windowWidth="24240" windowHeight="13020" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Plan1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="126" uniqueCount="62">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="130" uniqueCount="65">
   <si>
     <t>FACILIDADE</t>
   </si>
@@ -222,6 +222,15 @@
   </si>
   <si>
     <t>EDD RADIO IP (LIVRE)</t>
+  </si>
+  <si>
+    <t>5G_INDOOR</t>
+  </si>
+  <si>
+    <t>5G</t>
+  </si>
+  <si>
+    <t>5G INDOOR</t>
   </si>
 </sst>
 </file>
@@ -539,7 +548,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:G27"/>
+  <dimension ref="A1:G28"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="30.5546875" bestFit="1" customWidth="1"/>
@@ -1129,6 +1138,26 @@
         <v>8</v>
       </c>
     </row>
+    <row r="28" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A28">
+        <v>42</v>
+      </c>
+      <c r="B28" t="s">
+        <v>62</v>
+      </c>
+      <c r="D28" t="s">
+        <v>64</v>
+      </c>
+      <c r="E28" t="s">
+        <v>63</v>
+      </c>
+      <c r="F28" t="s">
+        <v>56</v>
+      </c>
+      <c r="G28">
+        <v>8</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
